--- a/test-data/gambling-sites-test.xlsx
+++ b/test-data/gambling-sites-test.xlsx
@@ -125,10 +125,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -160,10 +160,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -441,6 +441,12 @@
       <c r="A3" t="str">
         <v>afhaalchinees.be + derockerbikes.be</v>
       </c>
+      <c r="C3" t="str">
+        <v>Toevoeging zwarte lijst (website + mirrors) + kennisgeving ISP’s | Melding aan DNS BELGIUM</v>
+      </c>
+      <c r="E3" t="str">
+        <v>I086-2026</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -2707,6 +2713,9 @@
       <c r="A257" t="str">
         <v>vipluck15.com</v>
       </c>
+      <c r="B257" t="str">
+        <v>No access</v>
+      </c>
       <c r="E257" t="str">
         <v>I019-2026</v>
       </c>
@@ -2725,6 +2734,9 @@
     <row r="259">
       <c r="A259" t="str">
         <v>thorcasino.com</v>
+      </c>
+      <c r="B259" t="str">
+        <v>No access</v>
       </c>
       <c r="E259" t="str">
         <v>I022-2026</v>
